--- a/diseases/d112/2026-2029.xlsx
+++ b/diseases/d112/2026-2029.xlsx
@@ -14417,6 +14417,154 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
+      <c r="AT90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14450,7 +14598,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -14533,7 +14681,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -14543,7 +14691,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d112/2026-2029.xlsx
+++ b/diseases/d112/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -1061,9 +1058,6 @@
       <c r="O4" t="n">
         <v>19</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.1775527281373836</v>
       </c>
@@ -2937,9 +2931,6 @@
       <c r="O16" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -3085,9 +3076,6 @@
       <c r="O17" t="n">
         <v>8</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.07475904342626677</v>
       </c>
@@ -4813,9 +4801,6 @@
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -4961,9 +4946,6 @@
       <c r="O29" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.03737952171313338</v>
       </c>
@@ -6541,9 +6523,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6689,9 +6668,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -6837,9 +6813,6 @@
       <c r="O41" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -8417,9 +8390,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8565,9 +8535,6 @@
       <c r="O52" t="n">
         <v>1</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -8713,9 +8680,6 @@
       <c r="O53" t="n">
         <v>3</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.02803464128485004</v>
       </c>
@@ -10589,9 +10553,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10737,9 +10698,6 @@
       <c r="O66" t="n">
         <v>2</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -10885,9 +10843,6 @@
       <c r="O67" t="n">
         <v>3</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.02803464128485004</v>
       </c>
@@ -11281,9 +11236,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -11429,9 +11381,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -11577,9 +11526,6 @@
       <c r="O71" t="n">
         <v>1</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -11725,9 +11671,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -11873,9 +11816,6 @@
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -12021,9 +11961,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -12169,9 +12106,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -12317,9 +12251,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -12465,9 +12396,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12613,9 +12541,6 @@
       <c r="O78" t="n">
         <v>3</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.02803464128485004</v>
       </c>
@@ -13009,9 +12934,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -13157,9 +13079,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -13305,9 +13224,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -13453,9 +13369,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -13601,9 +13514,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -13749,9 +13659,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13897,9 +13804,6 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -14045,9 +13949,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -14193,9 +14094,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -14341,9 +14239,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -14487,9 +14382,6 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">

--- a/diseases/d112/2026-2029.xlsx
+++ b/diseases/d112/2026-2029.xlsx
@@ -14457,6 +14457,151 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr"/>
+      <c r="AT91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14490,7 +14635,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14718,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -14583,7 +14728,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d112/2026-2029.xlsx
+++ b/diseases/d112/2026-2029.xlsx
@@ -14602,6 +14602,151 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14635,7 +14780,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14718,7 +14863,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -14728,7 +14873,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d112/2026-2029.xlsx
+++ b/diseases/d112/2026-2029.xlsx
@@ -12497,12 +12497,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -12536,95 +12536,81 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>0.02803464128485004</v>
+        <v>0</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12651,7 +12637,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -12700,98 +12686,23 @@
       <c r="O79" t="n">
         <v>3</v>
       </c>
+      <c r="R79" t="n">
+        <v>0.02803464128485004</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U79" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>Papegojsjuka</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD79" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE79" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF79" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG79" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM psittacosis category.</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN79" t="b">
-        <v>1</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -12885,17 +12796,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -12920,7 +12831,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -12929,81 +12840,170 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Papegojsjuka</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM psittacosis category.</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN80" t="b">
+        <v>1</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -13035,12 +13035,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -13113,42 +13113,42 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -13180,12 +13180,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -13210,7 +13210,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -13258,42 +13258,42 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -13325,12 +13325,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -13403,42 +13403,42 @@
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -13470,12 +13470,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -13548,42 +13548,42 @@
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -13615,12 +13615,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -13693,42 +13693,42 @@
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -13760,12 +13760,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -13799,13 +13799,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -13838,42 +13838,42 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -13905,12 +13905,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -13944,13 +13944,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -13983,42 +13983,42 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14050,12 +14050,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -14128,42 +14128,42 @@
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -14195,12 +14195,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -14225,12 +14225,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -14273,42 +14273,42 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14340,12 +14340,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -14418,42 +14418,42 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14515,7 +14515,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -14742,6 +14742,151 @@
         </is>
       </c>
       <c r="BC92" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -14863,7 +15008,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -14873,7 +15018,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d112/2026-2029.xlsx
+++ b/diseases/d112/2026-2029.xlsx
@@ -10654,12 +10654,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -10693,17 +10693,14 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>2</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0.02710540560393419</v>
+        <v>0</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10732,42 +10729,42 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10799,12 +10796,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10838,95 +10835,78 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>3</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0.02803464128485004</v>
+        <v>0</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10953,17 +10933,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10997,170 +10977,78 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>3</v>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>Papegojsjuka</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD68" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE68" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF68" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG68" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM psittacosis category.</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN68" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP68" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
-        </is>
-      </c>
-      <c r="AT68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV68" t="inlineStr">
-        <is>
-          <t>fohm_sminet</t>
-        </is>
-      </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11192,12 +11080,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -11222,7 +11110,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -11236,12 +11124,9 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -11270,42 +11155,42 @@
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11337,12 +11222,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -11367,7 +11252,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -11381,12 +11266,9 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -11415,42 +11297,42 @@
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11482,12 +11364,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -11512,7 +11394,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -11521,17 +11403,14 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11560,42 +11439,42 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11627,12 +11506,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -11657,7 +11536,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -11666,13 +11545,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>0.02710540560393419</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -11705,42 +11584,42 @@
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11651,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11802,7 +11681,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -11811,81 +11690,95 @@
         </is>
       </c>
       <c r="N73" t="n">
+        <v>3</v>
+      </c>
+      <c r="O73" t="n">
+        <v>3</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0.02803464128485004</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="AT73" t="n">
         <v>1</v>
       </c>
-      <c r="O73" t="n">
-        <v>1</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP73" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
-      <c r="AT73" t="n">
-        <v>0</v>
-      </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -11912,17 +11805,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11947,7 +11840,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -11956,81 +11849,170 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Papegojsjuka</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM psittacosis category.</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN74" t="b">
+        <v>1</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -12092,7 +12074,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -12237,7 +12219,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -12352,12 +12334,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -12382,22 +12364,22 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -12430,42 +12412,42 @@
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12497,12 +12479,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -12527,12 +12509,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -12575,42 +12557,42 @@
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -12642,12 +12624,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -12672,104 +12654,90 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>0.02803464128485004</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12796,17 +12764,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -12831,179 +12799,90 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>3</v>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>Papegojsjuka</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD80" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE80" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF80" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG80" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM psittacosis category.</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN80" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -13065,12 +12944,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -13210,12 +13089,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -13325,12 +13204,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -13355,7 +13234,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -13364,13 +13243,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>0.007345623639039581</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -13403,42 +13282,42 @@
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13470,12 +13349,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -13500,7 +13379,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -13514,12 +13393,9 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -13548,42 +13424,42 @@
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13615,12 +13491,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -13645,7 +13521,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -13659,12 +13535,9 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -13693,42 +13566,42 @@
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13760,12 +13633,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -13790,7 +13663,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -13804,12 +13677,9 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -13838,42 +13708,42 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13905,12 +13775,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -13935,7 +13805,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -13944,17 +13814,14 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -13983,42 +13850,42 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14050,12 +13917,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -14080,7 +13947,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -14094,12 +13961,9 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -14128,42 +13992,42 @@
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14195,12 +14059,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -14225,7 +14089,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -14239,12 +14103,9 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -14273,42 +14134,42 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14340,12 +14201,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -14370,12 +14231,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N90" t="n">
@@ -14418,42 +14279,42 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14485,12 +14346,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -14515,90 +14376,104 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>0.02803464128485004</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -14625,17 +14500,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -14660,90 +14535,179 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Papegojsjuka</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM psittacosis category.</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN92" t="b">
+        <v>1</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -14805,12 +14769,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -14889,6 +14853,3172 @@
       <c r="BC93" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" t="n">
+        <v>1</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
+      <c r="AT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
+      <c r="AT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC108" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
+      <c r="AT109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr"/>
+      <c r="AT110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr"/>
+      <c r="AT111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr"/>
+      <c r="AT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr"/>
+      <c r="AT113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr"/>
+      <c r="AT114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
+      <c r="AT115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14925,7 +18055,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -15008,7 +18138,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10">
@@ -15018,7 +18148,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11">
@@ -15070,7 +18200,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
